--- a/fulltext_requests/fulltext_acquisition_2026-10-09.xlsx
+++ b/fulltext_requests/fulltext_acquisition_2026-10-09.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_click_to_download_61" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_click_to_download_16" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_maybe_free_14" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_unknown_check_18" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_library_request_153" sheetId="5" state="visible" r:id="rId5"/>
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -615,46 +615,49 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FS-001324</t>
+          <t>FS-002317</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Salivary IgA as a risk factor for upper respiratory infections in elite professional athletes.</t>
+          <t>Does proteinuria-inducing physical activity increase biomarkers of acute kidney injury?</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Medicine and science in sports and exercise</t>
+          <t>Kidney &amp; blood pressure research</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10.1249/mss.0b013e31816be9c3</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>10.1159/000343417</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://karger.com/kbr/article-pdf/36/1/278/3048436/000343417.pdf</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://dspace.lboro.ac.uk/2134/10614</t>
+          <t>https://doi.org/10.1159/000343417</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1249/mss.0b013e31816be9c3</t>
+          <t>https://doi.org/10.1159/000343417</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>FS-001324.pdf</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>FS-002317.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -664,50 +667,44 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FS-002317</t>
+          <t>FS-002536</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Does proteinuria-inducing physical activity increase biomarkers of acute kidney injury?</t>
+          <t>Cytokine kinetics in nasal mucosa and sera: new insights in understanding upper-airway disease of marathon runners.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Kidney &amp; blood pressure research</t>
+          <t>Exercise immunology review</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>10.1159/000343417</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>https://karger.com/kbr/article-pdf/36/1/278/3048436/000343417.pdf</t>
+          <t>10.22029/eir.2013.1677</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1159/000343417</t>
+          <t>http://repositorio.unifesp.br/handle/11600/43635</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1159/000343417</t>
+          <t>https://doi.org/10.22029/eir.2013.1677</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>FS-002317.pdf</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>FS-002536.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -717,46 +714,44 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FS-002536</t>
+          <t>FS-003210</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cytokine kinetics in nasal mucosa and sera: new insights in understanding upper-airway disease of marathon runners.</t>
+          <t>Changes of Hematological Markers during a Multi-stage Ultra-marathon Competition in the Heat.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Exercise immunology review</t>
+          <t>International journal of sports medicine</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10.22029/eir.2013.1677</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>10.1055/s-0035-1555929</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>http://repositorio.unifesp.br/handle/11600/43635</t>
+          <t>http://repositorio.unicamp.br/jspui/handle/REPOSIP/329563</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.22029/eir.2013.1677</t>
+          <t>https://doi.org/10.1055/s-0035-1555929</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>FS-002536.pdf</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>FS-003210.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -766,46 +761,49 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FS-002569</t>
+          <t>FS-004724</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Effects of aerobic exercise on lipid-effector molecules of the innate immune response.</t>
+          <t>Early Warning of Acute Altitude Sickness by Physiological Variables and Noninvasive Cardiovascular Indicators.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Medicine and science in sports and exercise</t>
+          <t>Chinese medical sciences journal = Chung-kuo i hsueh k'o hsueh tsa chih</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10.1249/mss.0000000000000137</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>10.24920/003552</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>http://cmsj.cams.cn/CN/article/downloadArticleFile.do?attachType=PDF&amp;id=3029</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/3974503</t>
+          <t>https://doi.org/10.24920/003552</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1249/mss.0000000000000137</t>
+          <t>https://doi.org/10.24920/003552</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>FS-002569.pdf</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>FS-004724.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -815,552 +813,524 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FS-003210</t>
+          <t>FS-011007</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Changes of Hematological Markers during a Multi-stage Ultra-marathon Competition in the Heat.</t>
+          <t>Lymphocyte HSP72 following exercise in hyperthermic runners: The effect of temperature</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>International journal of sports medicine</t>
+          <t>Journal of Thermal Biology</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10.1055/s-0035-1555929</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>10.1016/j.jtherbio.2007.07.001</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>http://repositorio.unicamp.br/jspui/handle/REPOSIP/329563</t>
+          <t>https://figshare.com/articles/journal_contribution/Lymphocyte_HSP72_following_exercise_in_hyperthermic_runners_the_effect_of_temperature/22886273</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1055/s-0035-1555929</t>
+          <t>https://doi.org/10.1016/j.jtherbio.2007.07.001</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>FS-003210.pdf</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>FS-011007.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FS-003468</t>
+          <t>FS-002638</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Short-term reliability of inflammatory mediators and response to exercise in the heat.</t>
+          <t>Rapid upregulation and clearance of distinct circulating microRNAs after prolonged aerobic exercise.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Journal of sports sciences</t>
+          <t>Journal of applied physiology (Bethesda, Md. : 1985)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10.1080/02640414.2016.1227464</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>10.1152/japplphysiol.01141.2013</t>
+        </is>
+      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>https://figshare.com/articles/journal_contribution/Short-term_reliability_of_inflammatory_mediators_and_response_to_exercise_in_the_heat/22186714</t>
+          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/3949215</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/02640414.2016.1227464</t>
+          <t>https://doi.org/10.1152/japplphysiol.01141.2013</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>FS-003468.pdf</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>FS-002638.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FS-003800</t>
+          <t>FS-002878</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Small RNA-seq during acute maximal exercise reveal RNAs involved in vascular inflammation and cardiometabolic health: brief report.</t>
+          <t>Dynamic changes in dna methylation status in peripheral blood Mononuclear cells following an acute bout of exercise: Potential impact of exercise-induced elevations in interleukin-6 concentration.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>American journal of physiology. Heart and circulatory physiology</t>
+          <t>Journal of biological regulators and homeostatic agents</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>10.1152/ajpheart.00500.2017</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>http://www.biolifesas.org/jbrha/abstractsjbrha28-3.pdf</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/5814647</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1152/ajpheart.00500.2017</t>
+          <t>http://nrl.northumbria.ac.uk/id/eprint/17753/</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>FS-003800.pdf</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>FS-002878.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FS-004179</t>
+          <t>FS-003073</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brief Report: Training Load, Salivary Immunoglobulin A, and Illness Incidence in Elite Paratriathletes.</t>
+          <t>Circulating inflammatory miRNA signature in response to different doses of aerobic exercise.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>International journal of sports physiology and performance</t>
+          <t>Journal of applied physiology (Bethesda, Md. : 1985)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10.1123/ijspp.2018-0439</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>10.1152/japplphysiol.00077.2015</t>
+        </is>
+      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>https://dspace.lboro.ac.uk/2134/34846</t>
+          <t>http://hdl.handle.net/10651/34131</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1123/ijspp.2018-0439</t>
+          <t>https://doi.org/10.1152/japplphysiol.00077.2015</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>FS-004179.pdf</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>FS-003073.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FS-004724</t>
+          <t>FS-005334</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Early Warning of Acute Altitude Sickness by Physiological Variables and Noninvasive Cardiovascular Indicators.</t>
+          <t>Air pollution and high-intensity interval exercise: Implications to anti-inflammatory balance, metabolome and cardiovascular responses.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Chinese medical sciences journal = Chung-kuo i hsueh k'o hsueh tsa chih</t>
+          <t>The Science of the total environment</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10.24920/003552</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>http://cmsj.cams.cn/CN/article/downloadArticleFile.do?attachType=PDF&amp;id=3029</t>
+          <t>10.1016/j.scitotenv.2021.151094</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.24920/003552</t>
+          <t>https://doi.org/10.1016/j.scitotenv.2021.151094</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.24920/003552</t>
+          <t>https://doi.org/10.1016/j.scitotenv.2021.151094</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>FS-004724.pdf</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>FS-005334.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FS-004989</t>
+          <t>FS-006651</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Improved recovery from skeletal muscle damage is largely unexplained by myofibrillar protein synthesis or inflammatory and regenerative gene expression pathways.</t>
+          <t>Exercise-induced β2-adrenergic receptor activation enhances effector lymphocyte mobilization in humans and suppresses lymphoma growth in mice through NK-cells.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>American journal of physiology. Endocrinology and metabolism</t>
+          <t>Brain, behavior, and immunity</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10.1152/ajpendo.00454.2020</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>10.1016/j.bbi.2025.04.040</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13034990/pdf/nihms-2148994.pdf</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/8260377</t>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13034990/</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1152/ajpendo.00454.2020</t>
+          <t>https://doi.org/10.1016/j.bbi.2025.04.040</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>FS-004989.pdf</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>FS-006651.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FS-005118</t>
+          <t>FS-000681</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Endotoxaemia in exhausted runners after a long-distance race.</t>
+          <t>CD94 expression and natural killer cell activity after acute exercise.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>South African medical journal = Suid-Afrikaanse tydskrif vir geneeskunde</t>
+          <t>Journal of science and medicine in sport</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1988</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>10.1016/s1440-2440(04)80015-x</t>
+        </is>
+      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/3375945/</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>https://doi.org/10.1016/s1440-2440(04)80015-x</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/s1440-2440(04)80015-x</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>FS-005118.pdf</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>FS-000681.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FS-007033</t>
+          <t>FS-000972</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lymphocyte subpopulations in healthy Ukrainian men: local reference ranges, long temporal stability, and exercise-induced variability.</t>
+          <t>Salivary IgA response of triathletes participating in the French Iron Tour.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Immunobiology</t>
+          <t>International journal of sports medicine</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>10.1016/j.imbio.2026.153170</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>10.1055/s-2005-865747</t>
+        </is>
+      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.imbio.2026.153170</t>
+          <t>https://hal.science/hal-03061834</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.imbio.2026.153170</t>
+          <t>https://doi.org/10.1055/s-2005-865747</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>FS-007033.pdf</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>FS-000972.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FS-007479</t>
+          <t>FS-002573</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>The effect on immunity of long-term intensive training in elite swimmers.</t>
+          <t>A common variation in the promoter region of interleukin-6 gene shows association with exercise performance.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Clinical and experimental immunology</t>
+          <t>Journal of sports science &amp; medicine</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>10.1111/j.1365-2249.1995.tb06658.x</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>2009</t>
+        </is>
+      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/1553334</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1111/j.1365-2249.1995.tb06658.x</t>
+          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/3761487</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>FS-007479.pdf</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>FS-002573.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FS-007953</t>
+          <t>FS-002841</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Machine Learning-based Classification of Exercise Status Using miR-21 Expression and Multivariable Participant Profiles</t>
+          <t>Influence of HMB supplementation and resistance training on cytokine responses to resistance exercise.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Biomedical and Biotechnology Research Journal</t>
+          <t>Journal of the American College of Nutrition</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>10.4103/bbrj.bbrj_72_26</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>10.1080/07315724.2014.911669</t>
+        </is>
+      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.4103/bbrj.bbrj_72_26</t>
+          <t>https://digitalcommons.uri.edu/kinesiology_facpubs/98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.4103/bbrj.bbrj_72_26</t>
+          <t>https://doi.org/10.1080/07315724.2014.911669</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>FS-007953.pdf</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>FS-002841.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FS-009361</t>
+          <t>FS-005508</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Changes of cardiac biomarkers in ultramarathon runners</t>
+          <t>C-Reactive Protein and Skin Temperature of the lower limbs of Brazilian elite soccer players like load markers following three consecutive games.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Physical Activity Review</t>
+          <t>Journal of thermal biology</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>10.16926/par.2019.07.11</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>10.1016/j.jtherbio.2022.103188</t>
+        </is>
+      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.16926/par.2019.07.11</t>
+          <t>https://doi.org/10.1016/j.jtherbio.2022.103188</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.16926/par.2019.07.11</t>
+          <t>https://doi.org/10.1016/j.jtherbio.2022.103188</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>FS-009361.pdf</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>FS-005508.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FS-010763</t>
+          <t>FS-010740</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Leukocyte, neutrophil, immature granulocyte counts and interleukin-6 are superior to procalcitonin, C-reactive protein and delta-He for detection of mild inflammation: Data from marathon runners producing mild systemic inflammation visible immediately after the run</t>
+          <t>Effect of sensory stimulation on salivary IgA secretion rate in karate players</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LaboratoriumsMedizin</t>
+          <t>Biology of Sport</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1370,2355 +1340,61 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>10.1515/JLM.2010.005</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.degruyter.com/document/doi/10.1515/jlm.2010.005/pdf</t>
+          <t>10.5604/20831862.927493</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1515/jlm.2010.005</t>
+          <t>https://doaj.org/article/610940cc85e14b1cafd2a2b920086fa8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1515/JLM.2010.005</t>
+          <t>https://doi.org/10.5604/20831862.927493</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>FS-010763.pdf</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>FS-011007</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Lymphocyte HSP72 following exercise in hyperthermic runners: The effect of temperature</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Journal of Thermal Biology</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>10.1016/j.jtherbio.2007.07.001</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>https://figshare.com/articles/journal_contribution/Lymphocyte_HSP72_following_exercise_in_hyperthermic_runners_the_effect_of_temperature/22886273</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.jtherbio.2007.07.001</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>FS-011007.pdf</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>FS-011033</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Muscle trauma and immune activation after a downhill marathon (Tyrolean Speed Marathon)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Pteridines</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>10.1515/pteridines.2006.17.4.121</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1515/pteridines.2006.17.4.121</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1515/pteridines.2006.17.4.121</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>FS-011033.pdf</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>FS-000645</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Effects of exercise on gene expression in human peripheral blood mononuclear cells.</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Journal of applied physiology (Bethesda, Md. : 1985)</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>10.1152/japplphysiol.00316.2004</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>https://escholarship.org/uc/item/4b7136mv</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1152/japplphysiol.00316.2004</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>FS-000645.pdf</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>FS-001211</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Effects of 30 min of aerobic exercise on gene expression in human neutrophils.</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Journal of applied physiology (Bethesda, Md. : 1985)</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>10.1152/japplphysiol.00872.2007</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>https://escholarship.org/uc/item/2vs4f8fz</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1152/japplphysiol.00872.2007</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>FS-001211.pdf</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>FS-001584</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Differential genomic responses in old vs. young humans despite similar levels of modest muscle damage after resistance loading.</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Physiological genomics</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>10.1152/physiolgenomics.00151.2009</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/2825766</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1152/physiolgenomics.00151.2009</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>FS-001584.pdf</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>FS-001635</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Evidence for microRNA involvement in exercise-associated neutrophil gene expression changes.</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Journal of applied physiology (Bethesda, Md. : 1985)</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>10.1152/japplphysiol.01291.2009</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/2904199</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1152/japplphysiol.01291.2009</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>FS-001635.pdf</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>FS-001918</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Changes in transcriptional output of human peripheral blood mononuclear cells following resistance exercise.</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>European journal of applied physiology</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>10.1007/s00421-011-1923-2</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/4358769</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1007/s00421-011-1923-2</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>FS-001918.pdf</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>FS-001987</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Dynamic regulation of circulating microRNA during acute exhaustive exercise and sustained aerobic exercise training.</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>The Journal of physiology</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>10.1113/jphysiol.2011.213363</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/3179997</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1113/jphysiol.2011.213363</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>FS-001987.pdf</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>FS-002032</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Induced sputum proteome in healthy subjects and asthmatic patients.</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>The Journal of allergy and clinical immunology</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>10.1016/j.jaci.2011.07.053</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/4065239</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.jaci.2011.07.053</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>FS-002032.pdf</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>FS-002059</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Resistance exercise training influences skeletal muscle immune activation: a microarray analysis.</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Journal of applied physiology (Bethesda, Md. : 1985)</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>10.1152/japplphysiol.00860.2011</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/3289427</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1152/japplphysiol.00860.2011</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>FS-002059.pdf</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>FS-002346</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Impact of brief exercise on peripheral blood NK cell gene and microRNA expression in young adults.</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Journal of applied physiology (Bethesda, Md. : 1985)</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>10.1152/japplphysiol.01341.2012</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/3615590</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1152/japplphysiol.01341.2012</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>FS-002346.pdf</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>FS-002554</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Human inflammatory and resolving lipid mediator responses to resistance exercise and ibuprofen treatment.</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>American journal of physiology. Regulatory, integrative and comparative physiology</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>10.1152/ajpregu.00128.2013</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/3882565</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1152/ajpregu.00128.2013</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>FS-002554.pdf</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>FS-002638</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Rapid upregulation and clearance of distinct circulating microRNAs after prolonged aerobic exercise.</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Journal of applied physiology (Bethesda, Md. : 1985)</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>10.1152/japplphysiol.01141.2013</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/3949215</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1152/japplphysiol.01141.2013</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>FS-002638.pdf</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>FS-002669</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Identification of human exercise-induced myokines using secretome analysis.</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Physiological genomics</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>10.1152/physiolgenomics.00174.2013</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>https://cris.maastrichtuniversity.nl/en/publications/81665948-25db-4b4d-8c9c-2ce4df71ad8c</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1152/physiolgenomics.00174.2013</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>FS-002669.pdf</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>FS-002878</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Dynamic changes in dna methylation status in peripheral blood Mononuclear cells following an acute bout of exercise: Potential impact of exercise-induced elevations in interleukin-6 concentration.</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Journal of biological regulators and homeostatic agents</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>http://www.biolifesas.org/jbrha/abstractsjbrha28-3.pdf</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>http://nrl.northumbria.ac.uk/id/eprint/17753/</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>FS-002878.pdf</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>FS-003073</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Circulating inflammatory miRNA signature in response to different doses of aerobic exercise.</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Journal of applied physiology (Bethesda, Md. : 1985)</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>10.1152/japplphysiol.00077.2015</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>http://hdl.handle.net/10651/34131</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1152/japplphysiol.00077.2015</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>FS-003073.pdf</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>FS-004509</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Effects of an acute bout of exercise on circulating extracellular vesicles: tissue-, sex-, and BMI-related differences.</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>International journal of obesity (2005)</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>10.1038/s41366-019-0460-7</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>http://hdl.handle.net/2434/679447</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1038/s41366-019-0460-7</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>FS-004509.pdf</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>FS-004513</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Interval Exercise Lowers Circulating CD105 Extracellular Vesicles in Prediabetes.</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Medicine and science in sports and exercise</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>10.1249/mss.0000000000002185</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/7024030</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1249/mss.0000000000002185</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>FS-004513.pdf</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>FS-005334</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Air pollution and high-intensity interval exercise: Implications to anti-inflammatory balance, metabolome and cardiovascular responses.</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>The Science of the total environment</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>10.1016/j.scitotenv.2021.151094</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.scitotenv.2021.151094</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.scitotenv.2021.151094</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>FS-005334.pdf</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>FS-005434</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Acute exercise decreases insulin-stimulated extracellular vesicles in conjunction with augmentation index in adults with obesity.</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>The Journal of physiology</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>10.1113/jp282274</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/9314457</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1113/jp282274</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>FS-005434.pdf</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>FS-006154</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Exercise-Induced Cell-Free DNA Correlates with Energy Expenditure in Multiple Exercise Protocols.</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Medicine and science in sports and exercise</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>10.1249/mss.0000000000003363</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1249/mss.0000000000003363</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1249/mss.0000000000003363</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>FS-006154.pdf</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>FS-006563</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Cellular deconstruction of the human skeletal muscle microenvironment identifies an exercise-induced histaminergic crosstalk.</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Cell metabolism</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>10.1016/j.cmet.2024.12.011</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.cmet.2024.12.011</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.cmet.2024.12.011</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>FS-006563.pdf</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>FS-006651</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Exercise-induced β2-adrenergic receptor activation enhances effector lymphocyte mobilization in humans and suppresses lymphoma growth in mice through NK-cells.</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Brain, behavior, and immunity</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>10.1016/j.bbi.2025.04.040</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13034990/pdf/nihms-2148994.pdf</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13034990/</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.bbi.2025.04.040</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>FS-006651.pdf</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>FS-006734</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Transcriptomic analyses of peripheral blood mononuclear cells reveal age-specific basal and acute exercise responsiveness differences in humans.</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>American journal of physiology. Endocrinology and metabolism</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>10.1152/ajpendo.00169.2025</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1152/ajpendo.00169.2025</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1152/ajpendo.00169.2025</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>FS-006734.pdf</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>FS-006861</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Exploratory analysis of the impact of sex on sputum proteomic response to inhaled wood smoke in humans.</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Toxicological sciences : an official journal of the Society of Toxicology</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>10.1093/toxsci/kfaf150</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12844565/</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1093/toxsci/kfaf150</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>FS-006861.pdf</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>FS-006965</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Oxylipin Responses during the Yukon Arctic Ultra: The Longest and Coldest Ultramarathon in the World.</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Military medicine</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>10.1093/milmed/usaf622</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12958460/pdf/nihms-2140477.pdf</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/41525801/</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1093/milmed/usaf622</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>FS-006965.pdf</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>FS-007188</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Long-Distance Trail Running Induces Inflammatory-Associated Protein, Lipid, and Purine Oxidation in Red Blood Cells.</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Blood red cells &amp; iron</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>10.1016/j.brci.2026.100055</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.brci.2026.100055</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.brci.2026.100055</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>FS-007188.pdf</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>FS-000681</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>CD94 expression and natural killer cell activity after acute exercise.</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Journal of science and medicine in sport</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>10.1016/s1440-2440(04)80015-x</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/s1440-2440(04)80015-x</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/s1440-2440(04)80015-x</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>FS-000681.pdf</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>FS-000912</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Serum concentrations of C reactive protein, alpha1 antitrypsin, and complement (C3, C4, C1 esterase inhibitor) before and during the Vuelta a Espańa.</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>British journal of sports medicine</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>10.1136/bjsm.2005.019489</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/2492037</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1136/bjsm.2005.019489</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>FS-000912.pdf</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>FS-000972</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Salivary IgA response of triathletes participating in the French Iron Tour.</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>International journal of sports medicine</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>10.1055/s-2005-865747</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>https://hal.science/hal-03061834</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1055/s-2005-865747</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>FS-000972.pdf</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>FS-001044</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Effects of bovine colostrum supplementation on immune variables in highly trained cyclists.</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Journal of applied physiology (Bethesda, Md. : 1985)</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>10.1152/japplphysiol.00553.2006</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>https://figshare.com/articles/journal_contribution/Effects_of_bovine_colostrum_supplementation_on_immune_variables_in_highly_trained_cyclists/22862243</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1152/japplphysiol.00553.2006</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>FS-001044.pdf</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>FS-001505</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Environmental conditions, air pollutants, and airway cells in runners: a longitudinal field study.</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Journal of sports sciences</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>10.1080/02640410902946493</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>http://hdl.handle.net/10447/39526</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1080/02640410902946493</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>FS-001505.pdf</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>FS-002511</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Salivary antimicrobial protein responses during multistage ultramarathon competition conducted in hot environmental conditions.</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Applied physiology, nutrition, and metabolism = Physiologie appliquee, nutrition et metabolisme</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>10.1139/apnm-2013-0005</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>https://pureportal.coventry.ac.uk/en/publications/9be92eb8-5bfc-4f29-af31-28ef42ad3e72</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1139/apnm-2013-0005</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>FS-002511.pdf</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>FS-002573</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>A common variation in the promoter region of interleukin-6 gene shows association with exercise performance.</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Journal of sports science &amp; medicine</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/3761487</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>FS-002573.pdf</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>FS-002578</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>The effect of tapering period on plasma pro-inflammatory cytokine levels and performance in elite male cyclists.</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Journal of sports science &amp; medicine</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/3761545</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>FS-002578.pdf</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>FS-002841</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Influence of HMB supplementation and resistance training on cytokine responses to resistance exercise.</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Journal of the American College of Nutrition</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>10.1080/07315724.2014.911669</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>https://digitalcommons.uri.edu/kinesiology_facpubs/98</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1080/07315724.2014.911669</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>FS-002841.pdf</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>FS-005508</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>C-Reactive Protein and Skin Temperature of the lower limbs of Brazilian elite soccer players like load markers following three consecutive games.</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Journal of thermal biology</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>10.1016/j.jtherbio.2022.103188</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.jtherbio.2022.103188</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.jtherbio.2022.103188</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>FS-005508.pdf</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>FS-006114</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Sex differences in mood, hormone and immune response to combatives training in West Point Cadets.</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Psychoneuroendocrinology</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>10.1016/j.psyneuen.2023.106656</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.psyneuen.2023.106656</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.psyneuen.2023.106656</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>FS-006114.pdf</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>FS-007097</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Cumulative increases in circulating mtDNA as a potential biomarker of brain injury in rugby union: a pilot study.</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Journal of science and medicine in sport</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>10.1016/j.jsams.2026.03.024</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.jsams.2026.03.024</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.jsams.2026.03.024</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>FS-007097.pdf</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>FS-007259</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Passive, Electromagnetic-Responsive Hydrogel Immunosensor for Exercise Intensity Monitoring Based on Sweat C-Reactive Protein.</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Advanced healthcare materials</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>10.1002/adhm.71454</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13495878/</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/adhm.71454</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>FS-007259.pdf</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>FS-008227</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Effects of Congested Matches and Training Schedules on Salivary Markers in Elite Futsal Players</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Applied Sciences (Switzerland)</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>10.3390/app14124968</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/app14124968</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/app14124968</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>FS-008227.pdf</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>FS-009633</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>The &lt;i&gt;Bifidobacterim bifidum&lt;/i&gt; (BIB2) Probiotic Increased Immune System Factors in Men Sprint Athletes</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>CURRENT NUTRITION &amp; FOOD SCIENCE</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>10.2174/1573401313666170725114130</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>https://openresearchlibrary.org/viewer/4b9c8991-43b0-47f6-8e4f-4518ace87506</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.2174/1573401313666170725114130</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>FS-009633.pdf</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>FS-010114</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Changes in naïve and memory T-cells in elite swimmers during a winter training season</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Brain, Behavior, and Immunity</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>10.1016/j.bbi.2014.01.002</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>https://figshare.com/articles/journal_contribution/Changes_in_na_ve_and_memory_T-cells_in_elite_swimmers_during_a_winter_training_season/9629546</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>https://figshare.com/articles/journal_contribution/Changes_in_na_ve_and_memory_T-cells_in_elite_swimmers_during_a_winter_training_season/9629546</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.bbi.2014.01.002</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>FS-010114.pdf</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>FS-010649</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Monitoring biological and psychological measures throughout an entire season in male handball players</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>European Journal of Sport Science</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>10.1080/17461391003699070</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>https://hdl.handle.net/10612/19195</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1080/17461391003699070</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>FS-010649.pdf</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>FS-010740</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Effect of sensory stimulation on salivary IgA secretion rate in karate players</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Biology of Sport</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>10.5604/20831862.927493</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>https://doaj.org/article/610940cc85e14b1cafd2a2b920086fa8</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.5604/20831862.927493</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
           <t>FS-010740.pdf</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3834,8 +1510,6 @@
           <t>10.1152/japplphysiol.01064.2002</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1152/japplphysiol.01064.2002</t>
@@ -3846,7 +1520,6 @@
           <t>FS-000472.pdf</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3879,8 +1552,6 @@
           <t>10.1152/physiolgenomics.00096.2005</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1152/physiolgenomics.00096.2005</t>
@@ -3891,7 +1562,6 @@
           <t>FS-000837.pdf</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3924,8 +1594,6 @@
           <t>10.1152/japplphysiol.00066.2006</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1152/japplphysiol.00066.2006</t>
@@ -3936,7 +1604,6 @@
           <t>FS-001024.pdf</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3969,8 +1636,6 @@
           <t>10.1152/japplphysiol.00143.2013</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1152/japplphysiol.00143.2013</t>
@@ -3981,7 +1646,6 @@
           <t>FS-002421.pdf</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4014,8 +1678,6 @@
           <t>10.1152/japplphysiol.00909.2013</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1152/japplphysiol.00909.2013</t>
@@ -4026,7 +1688,6 @@
           <t>FS-002618.pdf</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4059,8 +1720,6 @@
           <t>10.1152/physiolgenomics.00068.2015</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1152/physiolgenomics.00068.2015</t>
@@ -4071,7 +1730,6 @@
           <t>FS-003209.pdf</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4104,8 +1762,6 @@
           <t>10.1152/jappl.1999.87.4.1360</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1152/jappl.1999.87.4.1360</t>
@@ -4116,7 +1772,6 @@
           <t>FS-000076.pdf</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4149,8 +1804,6 @@
           <t>10.1152/japplphysiol.00242.2007</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1152/japplphysiol.00242.2007</t>
@@ -4161,7 +1814,6 @@
           <t>FS-001146.pdf</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4194,8 +1846,6 @@
           <t>10.1152/japplphysiol.00707.2007</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1152/japplphysiol.00707.2007</t>
@@ -4206,7 +1856,6 @@
           <t>FS-001172.pdf</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4239,8 +1888,6 @@
           <t>10.1152/japplphysiol.00954.2007</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1152/japplphysiol.00954.2007</t>
@@ -4251,7 +1898,6 @@
           <t>FS-001293.pdf</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4284,8 +1930,6 @@
           <t>10.1152/japplphysiol.00575.2010</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1152/japplphysiol.00575.2010</t>
@@ -4296,7 +1940,6 @@
           <t>FS-001833.pdf</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4329,8 +1972,6 @@
           <t>10.1152/jappl.1990.68.3.1069</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1152/jappl.1990.68.3.1069</t>
@@ -4341,7 +1982,6 @@
           <t>FS-001905.pdf</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4374,8 +2014,6 @@
           <t>10.1152/japplphysiol.00864.2011</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1152/japplphysiol.00864.2011</t>
@@ -4386,7 +2024,6 @@
           <t>FS-002079.pdf</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4419,8 +2056,6 @@
           <t>10.1152/japplphysiol.00115.2020</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1152/japplphysiol.00115.2020</t>
@@ -4431,7 +2066,6 @@
           <t>FS-005169.pdf</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -4564,8 +2198,6 @@
           <t>10.1139/h01-015</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1139/h01-015</t>
@@ -4576,7 +2208,6 @@
           <t>FS-000242.pdf</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4609,8 +2240,6 @@
           <t>10.1111/j.1365-2222.1979.tb02506.x</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1111/j.1365-2222.1979.tb02506.x</t>
@@ -4621,7 +2250,6 @@
           <t>FS-000266.pdf</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4654,8 +2282,6 @@
           <t>10.2116/analsci.17.593</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.2116/analsci.17.593</t>
@@ -4666,7 +2292,6 @@
           <t>FS-000287.pdf</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4694,16 +2319,11 @@
           <t>2004</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>FS-011064.pdf</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4736,8 +2356,6 @@
           <t>10.1092/BTWQ5YMYVQ67QK9L</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1092/BTWQ5YMYVQ67QK9L</t>
@@ -4748,7 +2366,6 @@
           <t>FS-013731.pdf</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4776,16 +2393,11 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>FS-004809.pdf</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4813,16 +2425,11 @@
           <t>1997</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>FS-007775.pdf</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4855,8 +2462,6 @@
           <t>10.19193/0393-6384_2021_2_168</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.19193/0393-6384_2021_2_168</t>
@@ -4867,7 +2472,6 @@
           <t>FS-009093.pdf</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4895,16 +2499,11 @@
           <t>2010</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>FS-010790.pdf</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4932,16 +2531,11 @@
           <t>1997</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>FS-011432.pdf</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4969,16 +2563,11 @@
           <t>1996</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>FS-011807.pdf</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5006,16 +2595,11 @@
           <t>1984</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>FS-011900.pdf</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5043,16 +2627,11 @@
           <t>1985</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>FS-012006.pdf</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5080,16 +2659,11 @@
           <t>1978</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>FS-012067.pdf</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5117,16 +2691,11 @@
           <t>2002</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>FS-012651.pdf</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5154,16 +2723,11 @@
           <t>2010</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>FS-013573.pdf</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5191,16 +2755,11 @@
           <t>2003</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>FS-015048.pdf</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5228,16 +2787,11 @@
           <t>2003</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>FS-015049.pdf</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -5361,8 +2915,6 @@
           <t>10.1007/s004210050034</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s004210050034</t>
@@ -5373,7 +2925,6 @@
           <t>FS-000102.pdf</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5406,8 +2957,6 @@
           <t>10.1097/00005768-200001000-00020</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1097/00005768-200001000-00020</t>
@@ -5418,7 +2967,6 @@
           <t>FS-000106.pdf</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5451,8 +2999,6 @@
           <t>10.1055/s-2000-313</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1055/s-2000-313</t>
@@ -5463,7 +3009,6 @@
           <t>FS-000142.pdf</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5496,8 +3041,6 @@
           <t>10.1097/00005768-200007000-00005</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1097/00005768-200007000-00005</t>
@@ -5508,7 +3051,6 @@
           <t>FS-000156.pdf</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5541,8 +3083,6 @@
           <t>10.1055/s-2001-11339</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1055/s-2001-11339</t>
@@ -5553,7 +3093,6 @@
           <t>FS-000212.pdf</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5586,8 +3125,6 @@
           <t>10.1055/s-2002-19375</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1055/s-2002-19375</t>
@@ -5598,7 +3135,6 @@
           <t>FS-000297.pdf</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5631,8 +3167,6 @@
           <t>10.1309/14ty-2tdj-1x0y-1v6v</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1309/14ty-2tdj-1x0y-1v6v</t>
@@ -5643,7 +3177,6 @@
           <t>FS-000404.pdf</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5676,8 +3209,6 @@
           <t>10.1055/s-2003-39096</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1055/s-2003-39096</t>
@@ -5688,7 +3219,6 @@
           <t>FS-000451.pdf</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5721,8 +3251,6 @@
           <t>10.1007/s00421-003-0881-8</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s00421-003-0881-8</t>
@@ -5733,7 +3261,6 @@
           <t>FS-000533.pdf</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5766,8 +3293,6 @@
           <t>10.1249/00005768-199212000-00008</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1249/00005768-199212000-00008</t>
@@ -5778,7 +3303,6 @@
           <t>FS-000573.pdf</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5811,8 +3335,6 @@
           <t>10.1055/s-2004-820953</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1055/s-2004-820953</t>
@@ -5823,7 +3345,6 @@
           <t>FS-000693.pdf</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5851,16 +3372,11 @@
           <t>2004</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>FS-000751.pdf</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5893,8 +3409,6 @@
           <t>10.1080/00365510510013587</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/00365510510013587</t>
@@ -5905,7 +3419,6 @@
           <t>FS-000829.pdf</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5938,8 +3451,6 @@
           <t>10.1249/01.mss.0000177064.65927.98</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1249/01.mss.0000177064.65927.98</t>
@@ -5950,7 +3461,6 @@
           <t>FS-000873.pdf</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5983,8 +3493,6 @@
           <t>10.1055/s-2005-837467</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1055/s-2005-837467</t>
@@ -5995,7 +3503,6 @@
           <t>FS-000885.pdf</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6023,16 +3530,11 @@
           <t>2006</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>FS-000951.pdf</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6065,8 +3567,6 @@
           <t>10.1309/1d62h6krftvqrj0a</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1309/1d62h6krftvqrj0a</t>
@@ -6077,7 +3577,6 @@
           <t>FS-001039.pdf</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6110,8 +3609,6 @@
           <t>10.1249/mss.0b013e31802dd74e</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1249/mss.0b013e31802dd74e</t>
@@ -6122,7 +3619,6 @@
           <t>FS-001117.pdf</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6155,8 +3651,6 @@
           <t>10.1007/s00421-007-0484-x</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s00421-007-0484-x</t>
@@ -6167,7 +3661,6 @@
           <t>FS-001140.pdf</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6200,8 +3693,6 @@
           <t>10.1016/j.bbi.2007.09.001</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.bbi.2007.09.001</t>
@@ -6212,7 +3703,6 @@
           <t>FS-001197.pdf</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6245,8 +3735,6 @@
           <t>10.1249/mss.0b013e318149f2aa</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1249/mss.0b013e318149f2aa</t>
@@ -6257,7 +3745,6 @@
           <t>FS-001207.pdf</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6290,8 +3777,6 @@
           <t>10.1007/s00421-008-0866-8</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s00421-008-0866-8</t>
@@ -6302,7 +3787,6 @@
           <t>FS-001364.pdf</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6335,8 +3819,6 @@
           <t>10.1111/j.1600-0722.2008.00558.x</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1111/j.1600-0722.2008.00558.x</t>
@@ -6347,7 +3829,6 @@
           <t>FS-001370.pdf</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6380,8 +3861,6 @@
           <t>10.1016/j.imbio.2009.05.001</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.imbio.2009.05.001</t>
@@ -6392,7 +3871,6 @@
           <t>FS-001489.pdf</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6425,8 +3903,6 @@
           <t>10.1007/s00421-009-1160-0</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s00421-009-1160-0</t>
@@ -6437,7 +3913,6 @@
           <t>FS-001536.pdf</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6470,8 +3945,6 @@
           <t>10.1136/bjsm.2009.062497</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1136/bjsm.2009.062497</t>
@@ -6482,7 +3955,6 @@
           <t>FS-001575.pdf</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6515,8 +3987,6 @@
           <t>10.1249/mss.0b013e3181ac7adb</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1249/mss.0b013e3181ac7adb</t>
@@ -6527,7 +3997,6 @@
           <t>FS-001612.pdf</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6560,8 +4029,6 @@
           <t>10.1097/jsm.0b013e3181cb4086</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1097/jsm.0b013e3181cb4086</t>
@@ -6572,7 +4039,6 @@
           <t>FS-001622.pdf</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6605,8 +4071,6 @@
           <t>10.1007/s00421-010-1548-x</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s00421-010-1548-x</t>
@@ -6617,7 +4081,6 @@
           <t>FS-001733.pdf</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6650,8 +4113,6 @@
           <t>10.1007/s00421-010-1754-6</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s00421-010-1754-6</t>
@@ -6662,7 +4123,6 @@
           <t>FS-001835.pdf</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6695,8 +4155,6 @@
           <t>10.1021/pr2005555</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1021/pr2005555</t>
@@ -6707,7 +4165,6 @@
           <t>FS-002021.pdf</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6740,8 +4197,6 @@
           <t>10.1007/s00421-012-2490-x</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s00421-012-2490-x</t>
@@ -6752,7 +4207,6 @@
           <t>FS-002265.pdf</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6785,8 +4239,6 @@
           <t>10.1007/bf00572187</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/bf00572187</t>
@@ -6797,7 +4249,6 @@
           <t>FS-002301.pdf</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6830,8 +4281,6 @@
           <t>10.1007/s00418-012-1061-x</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s00418-012-1061-x</t>
@@ -6842,7 +4291,6 @@
           <t>FS-002327.pdf</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6875,8 +4323,6 @@
           <t>10.1016/j.molimm.2014.03.004</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.molimm.2014.03.004</t>
@@ -6887,7 +4333,6 @@
           <t>FS-002764.pdf</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6920,8 +4365,6 @@
           <t>10.55460/rrpw-rtln</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.55460/rrpw-rtln</t>
@@ -6932,7 +4375,6 @@
           <t>FS-003108.pdf</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6965,8 +4407,6 @@
           <t>10.1089/ham.2015.0098</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1089/ham.2015.0098</t>
@@ -6977,7 +4417,6 @@
           <t>FS-003254.pdf</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -7010,8 +4449,6 @@
           <t>10.23736/s0022-4707.16.06785-2</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.23736/s0022-4707.16.06785-2</t>
@@ -7022,7 +4459,6 @@
           <t>FS-003532.pdf</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -7055,8 +4491,6 @@
           <t>10.1016/j.wem.2016.12.001</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.wem.2016.12.001</t>
@@ -7067,7 +4501,6 @@
           <t>FS-003615.pdf</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -7100,8 +4533,6 @@
           <t>10.1002/mus.25687</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1002/mus.25687</t>
@@ -7112,7 +4543,6 @@
           <t>FS-003691.pdf</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -7145,8 +4575,6 @@
           <t>10.1007/s00421-017-3783-x</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s00421-017-3783-x</t>
@@ -7157,7 +4585,6 @@
           <t>FS-003901.pdf</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -7190,8 +4617,6 @@
           <t>10.1080/10715762.2018.1481288</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/10715762.2018.1481288</t>
@@ -7202,7 +4627,6 @@
           <t>FS-004098.pdf</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -7235,8 +4659,6 @@
           <t>10.1016/j.exger.2020.111026</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.exger.2020.111026</t>
@@ -7247,7 +4669,6 @@
           <t>FS-004839.pdf</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -7280,8 +4701,6 @@
           <t>10.1016/j.advms.2024.09.003</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.advms.2024.09.003</t>
@@ -7292,7 +4711,6 @@
           <t>FS-006410.pdf</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -7325,8 +4743,6 @@
           <t>10.23736/s0022-4707.24.16227-5</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.23736/s0022-4707.24.16227-5</t>
@@ -7337,7 +4753,6 @@
           <t>FS-006499.pdf</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -7370,8 +4785,6 @@
           <t>10.1016/0091-6749(84)90296-3</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/0091-6749(84)90296-3</t>
@@ -7382,7 +4795,6 @@
           <t>FS-007384.pdf</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -7415,8 +4827,6 @@
           <t>10.1093/ajcp/77.3.285</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1093/ajcp/77.3.285</t>
@@ -7427,7 +4837,6 @@
           <t>FS-007440.pdf</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -7460,8 +4869,6 @@
           <t>10.1249/00005768-199502000-00008</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1249/00005768-199502000-00008</t>
@@ -7472,7 +4879,6 @@
           <t>FS-007508.pdf</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -7505,8 +4911,6 @@
           <t>10.1055/s-2007-1021134</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1055/s-2007-1021134</t>
@@ -7517,7 +4921,6 @@
           <t>FS-007530.pdf</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7550,8 +4953,6 @@
           <t>10.1093/clinids/18.supplement_1.s142</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1093/clinids/18.supplement_1.s142</t>
@@ -7562,7 +4963,6 @@
           <t>FS-007565.pdf</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7595,8 +4995,6 @@
           <t>10.1007/bf00376664</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/bf00376664</t>
@@ -7607,7 +5005,6 @@
           <t>FS-007578.pdf</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7640,8 +5037,6 @@
           <t>10.1111/j.1398-9995.1995.tb02497.x</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1111/j.1398-9995.1995.tb02497.x</t>
@@ -7652,7 +5047,6 @@
           <t>FS-007641.pdf</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7685,8 +5079,6 @@
           <t>10.1016/s0735-6757(98)90023-7</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/s0735-6757(98)90023-7</t>
@@ -7697,7 +5089,6 @@
           <t>FS-007778.pdf</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7730,8 +5121,6 @@
           <t>10.1097/00005768-199807000-00021</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1097/00005768-199807000-00021</t>
@@ -7742,7 +5131,6 @@
           <t>FS-007801.pdf</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7775,8 +5163,6 @@
           <t>10.1080/17461391.2023.2203107</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/17461391.2023.2203107</t>
@@ -7787,7 +5173,6 @@
           <t>FS-008737.pdf</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7820,8 +5205,6 @@
           <t>10.1039/c7ay01676j</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1039/c7ay01676j</t>
@@ -7832,7 +5215,6 @@
           <t>FS-009509.pdf</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7865,8 +5247,6 @@
           <t>10.5604/965481</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.5604/965481</t>
@@ -7877,7 +5257,6 @@
           <t>FS-010457.pdf</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -7910,8 +5289,6 @@
           <t>10.1007/s00421-011-1966-4</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s00421-011-1966-4</t>
@@ -7922,7 +5299,6 @@
           <t>FS-010465.pdf</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7955,8 +5331,6 @@
           <t>10.1249/01.mss.0000064964.80040.e9</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1249/01.mss.0000064964.80040.e9</t>
@@ -7967,7 +5341,6 @@
           <t>FS-011327.pdf</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7995,16 +5368,11 @@
           <t>1993</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>FS-011687.pdf</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -8037,8 +5405,6 @@
           <t>10.1016/s0021-8707(37)90440-4</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/s0021-8707(37)90440-4</t>
@@ -8049,7 +5415,6 @@
           <t>FS-013023.pdf</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -8082,8 +5447,6 @@
           <t>10.1016/s0047-6374(00)00178-0</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/s0047-6374(00)00178-0</t>
@@ -8094,7 +5457,6 @@
           <t>FS-000182.pdf</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -8127,8 +5489,6 @@
           <t>10.1123/ijsnem.11.s1.s9</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1123/ijsnem.11.s1.s9</t>
@@ -8139,7 +5499,6 @@
           <t>FS-000319.pdf</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -8172,8 +5531,6 @@
           <t>10.1096/fj.04-3063fje</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1096/fj.04-3063fje</t>
@@ -8184,7 +5541,6 @@
           <t>FS-000816.pdf</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -8217,8 +5573,6 @@
           <t>10.1016/j.bbrc.2009.11.150</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.bbrc.2009.11.150</t>
@@ -8229,7 +5583,6 @@
           <t>FS-001595.pdf</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -8262,8 +5615,6 @@
           <t>10.3109/13547500903502802</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.3109/13547500903502802</t>
@@ -8274,7 +5625,6 @@
           <t>FS-001615.pdf</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -8307,8 +5657,6 @@
           <t>10.1007/s00421-011-2048-3</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s00421-011-2048-3</t>
@@ -8319,7 +5667,6 @@
           <t>FS-001994.pdf</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -8352,8 +5699,6 @@
           <t>10.1002/eji.201141907</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1002/eji.201141907</t>
@@ -8364,7 +5709,6 @@
           <t>FS-002156.pdf</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -8397,8 +5741,6 @@
           <t>10.1002/ajhb.22311</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1002/ajhb.22311</t>
@@ -8409,7 +5751,6 @@
           <t>FS-002241.pdf</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -8442,8 +5783,6 @@
           <t>10.1007/s00421-013-2650-7</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s00421-013-2650-7</t>
@@ -8454,7 +5793,6 @@
           <t>FS-002435.pdf</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -8487,8 +5825,6 @@
           <t>10.1016/j.jprot.2013.12.004</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.jprot.2013.12.004</t>
@@ -8499,7 +5835,6 @@
           <t>FS-002619.pdf</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -8532,8 +5867,6 @@
           <t>10.1016/j.bbi.2013.10.023</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.bbi.2013.10.023</t>
@@ -8544,7 +5877,6 @@
           <t>FS-002666.pdf</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -8577,8 +5909,6 @@
           <t>10.1016/j.ymeth.2018.11.012</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.ymeth.2018.11.012</t>
@@ -8589,7 +5919,6 @@
           <t>FS-004231.pdf</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8622,8 +5951,6 @@
           <t>10.1111/hepr.13670</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1111/hepr.13670</t>
@@ -8634,7 +5961,6 @@
           <t>FS-005183.pdf</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -8667,8 +5993,6 @@
           <t>10.1249/mss.0000000000003130</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1249/mss.0000000000003130</t>
@@ -8679,7 +6003,6 @@
           <t>FS-005856.pdf</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8712,8 +6035,6 @@
           <t>10.1007/s10974-024-09668-6</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s10974-024-09668-6</t>
@@ -8724,7 +6045,6 @@
           <t>FS-006260.pdf</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8757,8 +6077,6 @@
           <t>10.1249/mss.0000000000003483</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1249/mss.0000000000003483</t>
@@ -8769,7 +6087,6 @@
           <t>FS-006296.pdf</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -8802,8 +6119,6 @@
           <t>10.1016/j.cell.2025.06.001</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.cell.2025.06.001</t>
@@ -8814,7 +6129,6 @@
           <t>FS-006706.pdf</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8847,8 +6161,6 @@
           <t>10.1016/j.jprot.2025.105587</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.jprot.2025.105587</t>
@@ -8859,7 +6171,6 @@
           <t>FS-006949.pdf</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8892,8 +6203,6 @@
           <t>10.1016/j.jtherbio.2011.03.013</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.jtherbio.2011.03.013</t>
@@ -8904,7 +6213,6 @@
           <t>FS-010498.pdf</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8932,16 +6240,11 @@
           <t>2012</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>FS-010564.pdf</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8974,8 +6277,6 @@
           <t>10.1097/00005768-199908000-00019</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1097/00005768-199908000-00019</t>
@@ -8986,7 +6287,6 @@
           <t>FS-000059.pdf</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -9019,8 +6319,6 @@
           <t>10.1097/00005768-200110000-00018</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1097/00005768-200110000-00018</t>
@@ -9031,7 +6329,6 @@
           <t>FS-000274.pdf</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -9064,8 +6361,6 @@
           <t>10.1097/00042752-200209000-00008</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1097/00042752-200209000-00008</t>
@@ -9076,7 +6371,6 @@
           <t>FS-000389.pdf</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -9109,8 +6403,6 @@
           <t>10.1055/s-2003-37194</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1055/s-2003-37194</t>
@@ -9121,7 +6413,6 @@
           <t>FS-000425.pdf</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -9154,8 +6445,6 @@
           <t>10.1055/s-2003-39095</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1055/s-2003-39095</t>
@@ -9166,7 +6455,6 @@
           <t>FS-000450.pdf</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -9199,8 +6487,6 @@
           <t>10.1055/s-2007-1021252</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1055/s-2007-1021252</t>
@@ -9211,7 +6497,6 @@
           <t>FS-000719.pdf</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -9244,8 +6529,6 @@
           <t>10.1111/j.1365-2257.2004.00642.x</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1111/j.1365-2257.2004.00642.x</t>
@@ -9256,7 +6539,6 @@
           <t>FS-000726.pdf</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -9289,8 +6571,6 @@
           <t>10.1055/s-2005-837489</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1055/s-2005-837489</t>
@@ -9301,7 +6581,6 @@
           <t>FS-000925.pdf</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -9334,8 +6613,6 @@
           <t>10.1080/02640410500141158</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/02640410500141158</t>
@@ -9346,7 +6623,6 @@
           <t>FS-000953.pdf</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -9379,8 +6655,6 @@
           <t>10.1055/s-2005-865858</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1055/s-2005-865858</t>
@@ -9391,7 +6665,6 @@
           <t>FS-000983.pdf</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -9424,8 +6697,6 @@
           <t>10.1373/clinchem.2006.070417</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1373/clinchem.2006.070417</t>
@@ -9436,7 +6707,6 @@
           <t>FS-000990.pdf</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9469,8 +6739,6 @@
           <t>10.1002/bio.922</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1002/bio.922</t>
@@ -9481,7 +6749,6 @@
           <t>FS-000995.pdf</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -9514,8 +6781,6 @@
           <t>10.1249/mss.0b013e318076b566</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
       <c r="I95" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1249/mss.0b013e318076b566</t>
@@ -9526,7 +6791,6 @@
           <t>FS-001176.pdf</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -9559,8 +6823,6 @@
           <t>10.1515/cclm.2008.050</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
       <c r="I96" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1515/cclm.2008.050</t>
@@ -9571,7 +6833,6 @@
           <t>FS-001269.pdf</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9604,8 +6865,6 @@
           <t>10.1139/h07-177</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
       <c r="I97" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1139/h07-177</t>
@@ -9616,7 +6875,6 @@
           <t>FS-001280.pdf</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -9649,8 +6907,6 @@
           <t>10.1136/bjsm.2008.047530</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1136/bjsm.2008.047530</t>
@@ -9661,7 +6917,6 @@
           <t>FS-001310.pdf</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -9694,8 +6949,6 @@
           <t>10.1007/s00421-008-0839-y</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s00421-008-0839-y</t>
@@ -9706,7 +6959,6 @@
           <t>FS-001339.pdf</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -9739,8 +6991,6 @@
           <t>10.1080/02640410802123177</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/02640410802123177</t>
@@ -9751,7 +7001,6 @@
           <t>FS-001372.pdf</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -9784,8 +7033,6 @@
           <t>10.1016/j.atherosclerosis.2009.10.025</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.atherosclerosis.2009.10.025</t>
@@ -9796,7 +7043,6 @@
           <t>FS-001598.pdf</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -9829,8 +7075,6 @@
           <t>10.1055/s-2007-1024777</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
       <c r="I102" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1055/s-2007-1024777</t>
@@ -9841,7 +7085,6 @@
           <t>FS-001904.pdf</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -9874,8 +7117,6 @@
           <t>10.1249/mss.0b013e3182408639</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
       <c r="I103" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1249/mss.0b013e3182408639</t>
@@ -9886,7 +7127,6 @@
           <t>FS-002071.pdf</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -9919,8 +7159,6 @@
           <t>10.1007/s00421-011-2273-9</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
       <c r="I104" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s00421-011-2273-9</t>
@@ -9931,7 +7169,6 @@
           <t>FS-002077.pdf</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -9959,16 +7196,11 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
           <t>FS-002088.pdf</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -10001,8 +7233,6 @@
           <t>10.1249/mss.0b013e318243253d</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
       <c r="I106" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1249/mss.0b013e318243253d</t>
@@ -10013,7 +7243,6 @@
           <t>FS-002172.pdf</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -10046,8 +7275,6 @@
           <t>10.1515/cclm-2011-0857</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
       <c r="I107" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1515/cclm-2011-0857</t>
@@ -10058,7 +7285,6 @@
           <t>FS-002180.pdf</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -10091,8 +7317,6 @@
           <t>10.1519/jsc.0000000000000380</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
       <c r="I108" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1519/jsc.0000000000000380</t>
@@ -10103,7 +7327,6 @@
           <t>FS-002641.pdf</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -10136,8 +7359,6 @@
           <t>10.1097/jsm.0000000000000122</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1097/jsm.0000000000000122</t>
@@ -10148,7 +7369,6 @@
           <t>FS-002803.pdf</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -10181,8 +7401,6 @@
           <t>10.1249/mss.0000000000000568</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
       <c r="I110" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1249/mss.0000000000000568</t>
@@ -10193,7 +7411,6 @@
           <t>FS-002906.pdf</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -10226,8 +7443,6 @@
           <t>10.1055/s-0034-1389904</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
       <c r="I111" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1055/s-0034-1389904</t>
@@ -10238,7 +7453,6 @@
           <t>FS-002940.pdf</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -10271,8 +7485,6 @@
           <t>10.1123/ijspp.2014-0493</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
       <c r="I112" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1123/ijspp.2014-0493</t>
@@ -10283,7 +7495,6 @@
           <t>FS-002948.pdf</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -10316,8 +7527,6 @@
           <t>10.1080/17461391.2015.1029982</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
       <c r="I113" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/17461391.2015.1029982</t>
@@ -10328,7 +7537,6 @@
           <t>FS-003030.pdf</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -10361,8 +7569,6 @@
           <t>10.1007/s00421-015-3245-2</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
       <c r="I114" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s00421-015-3245-2</t>
@@ -10373,7 +7579,6 @@
           <t>FS-003173.pdf</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -10406,8 +7611,6 @@
           <t>10.1007/s00421-015-3291-9</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
       <c r="I115" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s00421-015-3291-9</t>
@@ -10418,7 +7621,6 @@
           <t>FS-003224.pdf</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -10451,8 +7653,6 @@
           <t>10.1136/oemed-2015-103254</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
       <c r="I116" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1136/oemed-2015-103254</t>
@@ -10463,7 +7663,6 @@
           <t>FS-003274.pdf</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -10496,8 +7695,6 @@
           <t>10.1113/ep085795</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
       <c r="I117" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1113/ep085795</t>
@@ -10508,7 +7705,6 @@
           <t>FS-003334.pdf</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -10541,8 +7737,6 @@
           <t>10.1007/s11739-017-1653-5</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
       <c r="I118" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s11739-017-1653-5</t>
@@ -10553,7 +7747,6 @@
           <t>FS-003642.pdf</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -10586,8 +7779,6 @@
           <t>10.23736/s0022-4707.17.06943-2</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
       <c r="I119" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.23736/s0022-4707.17.06943-2</t>
@@ -10598,7 +7789,6 @@
           <t>FS-003815.pdf</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -10631,8 +7821,6 @@
           <t>10.1007/s00421-017-3746-2</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
       <c r="I120" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s00421-017-3746-2</t>
@@ -10643,7 +7831,6 @@
           <t>FS-003840.pdf</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -10676,8 +7863,6 @@
           <t>10.1123/ijspp.2017-0683</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
       <c r="I121" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1123/ijspp.2017-0683</t>
@@ -10688,7 +7873,6 @@
           <t>FS-003879.pdf</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -10721,8 +7905,6 @@
           <t>10.1080/02640414.2018.1521712</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
       <c r="I122" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/02640414.2018.1521712</t>
@@ -10733,7 +7915,6 @@
           <t>FS-004154.pdf</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -10766,8 +7947,6 @@
           <t>10.1080/17461391.2019.1585478</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
       <c r="I123" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/17461391.2019.1585478</t>
@@ -10778,7 +7957,6 @@
           <t>FS-004361.pdf</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -10811,8 +7989,6 @@
           <t>10.23736/s0022-4707.19.10096-5</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
       <c r="I124" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.23736/s0022-4707.19.10096-5</t>
@@ -10823,7 +7999,6 @@
           <t>FS-004537.pdf</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -10856,8 +8031,6 @@
           <t>10.3233/bmr-181363</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr"/>
       <c r="I125" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.3233/bmr-181363</t>
@@ -10868,7 +8041,6 @@
           <t>FS-004568.pdf</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -10901,8 +8073,6 @@
           <t>10.1519/jsc.0000000000003516</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
       <c r="I126" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1519/jsc.0000000000003516</t>
@@ -10913,7 +8083,6 @@
           <t>FS-004666.pdf</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -10946,8 +8115,6 @@
           <t>10.1007/5584_2020_546</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
       <c r="I127" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/5584_2020_546</t>
@@ -10958,7 +8125,6 @@
           <t>FS-004773.pdf</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -10991,8 +8157,6 @@
           <t>10.1080/19390211.2020.1786206</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
       <c r="I128" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/19390211.2020.1786206</t>
@@ -11003,7 +8167,6 @@
           <t>FS-004819.pdf</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -11036,8 +8199,6 @@
           <t>10.1007/s00421-020-04528-w</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
       <c r="I129" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s00421-020-04528-w</t>
@@ -11048,7 +8209,6 @@
           <t>FS-004954.pdf</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -11076,16 +8236,11 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
           <t>FS-005304.pdf</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -11118,8 +8273,6 @@
           <t>10.1093/gerona/glae001</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
       <c r="I131" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1093/gerona/glae001</t>
@@ -11130,7 +8283,6 @@
           <t>FS-006172.pdf</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -11163,8 +8315,6 @@
           <t>10.1113/jp287749</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr"/>
       <c r="I132" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1113/jp287749</t>
@@ -11175,7 +8325,6 @@
           <t>FS-006462.pdf</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -11208,8 +8357,6 @@
           <t>10.1055/a-2899-8817</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
       <c r="I133" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1055/a-2899-8817</t>
@@ -11220,7 +8367,6 @@
           <t>FS-007241.pdf</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -11253,8 +8399,6 @@
           <t>10.1016/j.jsams.2026.09.002</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
       <c r="I134" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.jsams.2026.09.002</t>
@@ -11265,7 +8409,6 @@
           <t>FS-007330.pdf</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -11293,16 +8436,11 @@
           <t>1983</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>FS-007404.pdf</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -11335,8 +8473,6 @@
           <t>10.1056/nejm198105213042106</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
       <c r="I136" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1056/nejm198105213042106</t>
@@ -11347,7 +8483,6 @@
           <t>FS-007452.pdf</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -11380,8 +8515,6 @@
           <t>10.1007/bf00618492</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
       <c r="I137" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/bf00618492</t>
@@ -11392,7 +8525,6 @@
           <t>FS-007501.pdf</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -11425,8 +8557,6 @@
           <t>10.1055/s-2007-1021126</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr"/>
       <c r="I138" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1055/s-2007-1021126</t>
@@ -11437,7 +8567,6 @@
           <t>FS-007528.pdf</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -11470,8 +8599,6 @@
           <t>10.3109/00207459309000609</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
       <c r="I139" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.3109/00207459309000609</t>
@@ -11482,7 +8609,6 @@
           <t>FS-007602.pdf</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -11515,8 +8641,6 @@
           <t>10.1055/s-2007-972833</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
       <c r="I140" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1055/s-2007-972833</t>
@@ -11527,7 +8651,6 @@
           <t>FS-007639.pdf</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -11560,8 +8683,6 @@
           <t>10.1152/ajpregu.1996.271.1.r222</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
-      <c r="H141" t="inlineStr"/>
       <c r="I141" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1152/ajpregu.1996.271.1.r222</t>
@@ -11572,7 +8693,6 @@
           <t>FS-007642.pdf</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -11605,8 +8725,6 @@
           <t>10.1097/00005768-199806000-00013</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr"/>
       <c r="I142" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1097/00005768-199806000-00013</t>
@@ -11617,7 +8735,6 @@
           <t>FS-007796.pdf</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -11650,8 +8767,6 @@
           <t>10.1038/s41590-023-01626-7</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr"/>
       <c r="I143" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1038/s41590-023-01626-7</t>
@@ -11662,7 +8777,6 @@
           <t>FS-008584.pdf</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -11695,8 +8809,6 @@
           <t>10.1177/1747954118779656</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
-      <c r="H144" t="inlineStr"/>
       <c r="I144" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1177/1747954118779656</t>
@@ -11707,7 +8819,6 @@
           <t>FS-009341.pdf</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -11740,8 +8851,6 @@
           <t>10.23736/s0022-4707.16.06390-8</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
       <c r="I145" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.23736/s0022-4707.16.06390-8</t>
@@ -11752,7 +8861,6 @@
           <t>FS-009525.pdf</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -11785,8 +8893,6 @@
           <t>10.1002/bio.1390</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
       <c r="I146" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1002/bio.1390</t>
@@ -11797,7 +8903,6 @@
           <t>FS-010351.pdf</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -11830,8 +8935,6 @@
           <t>10.1007/s00421-011-2003-3</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
       <c r="I147" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s00421-011-2003-3</t>
@@ -11842,7 +8945,6 @@
           <t>FS-010516.pdf</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -11875,8 +8977,6 @@
           <t>10.1080/17461390802251844</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
       <c r="I148" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/17461390802251844</t>
@@ -11887,7 +8987,6 @@
           <t>FS-010849.pdf</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -11920,8 +9019,6 @@
           <t>10.1016/j.scispo.2006.09.005</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
       <c r="I149" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.scispo.2006.09.005</t>
@@ -11932,7 +9029,6 @@
           <t>FS-010873.pdf</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -11965,8 +9061,6 @@
           <t>10.12968/bjtr.2000.7.12.13831</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
       <c r="I150" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.12968/bjtr.2000.7.12.13831</t>
@@ -11977,7 +9071,6 @@
           <t>FS-011412.pdf</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -12005,16 +9098,11 @@
           <t>2001</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
           <t>FS-011580.pdf</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -12047,8 +9135,6 @@
           <t>10.1080/15438629009511887</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
       <c r="I152" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/15438629009511887</t>
@@ -12059,7 +9145,6 @@
           <t>FS-011962.pdf</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -12087,16 +9172,11 @@
           <t>1990</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
           <t>FS-011982.pdf</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -12124,16 +9204,11 @@
           <t>1995</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr"/>
-      <c r="H154" t="inlineStr"/>
-      <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
           <t>FS-013867.pdf</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
